--- a/data/trans_bre/P2C_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,27</t>
+          <t>1,52; 8,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,96</t>
+          <t>-0,79; 7,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,07</t>
+          <t>1,54; 10,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,95</t>
+          <t>4,33; 12,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 41,89</t>
+          <t>6,24; 45,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 21,02</t>
+          <t>-1,95; 21,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 39,54</t>
+          <t>5,28; 43,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 77,91</t>
+          <t>21,05; 77,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,38</t>
+          <t>3,45; 10,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,94</t>
+          <t>6,49; 12,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,18</t>
+          <t>5,03; 10,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 33,98</t>
+          <t>3,73; 31,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 32,69</t>
+          <t>9,82; 33,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 27,71</t>
+          <t>13,15; 27,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 35,95</t>
+          <t>14,59; 35,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,5; 350,5</t>
+          <t>30,91; 350,81</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 13,37</t>
+          <t>1,25; 13,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 17,81</t>
+          <t>3,42; 17,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 15,51</t>
+          <t>3,56; 15,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,15</t>
+          <t>-2,87; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 48,77</t>
+          <t>3,69; 50,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 47,81</t>
+          <t>7,49; 47,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 55,75</t>
+          <t>10,8; 55,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 50,76</t>
+          <t>-22,76; 45,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,64</t>
+          <t>3,11; 7,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,16</t>
+          <t>4,37; 9,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,71</t>
+          <t>5,32; 9,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,54</t>
+          <t>4,18; 24,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,14</t>
+          <t>10,26; 27,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 21,26</t>
+          <t>9,45; 21,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 31,91</t>
+          <t>16,55; 32,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,98; 233,45</t>
+          <t>32,67; 219,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,48</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,85</t>
+          <t>0,92; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,96</t>
+          <t>-0,57; 7,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,65</t>
+          <t>1,54; 10,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,03</t>
+          <t>5,28; 13,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 45,56</t>
+          <t>4,09; 41,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 21,37</t>
+          <t>-1,42; 20,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 43,07</t>
+          <t>5,04; 40,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,05; 77,6</t>
+          <t>26,46; 90,05</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>110,17%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,4</t>
+          <t>3,51; 10,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,82</t>
+          <t>6,42; 13,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,98</t>
+          <t>4,98; 11,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 31,76</t>
+          <t>1,22; 5,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 33,05</t>
+          <t>10,11; 33,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 27,81</t>
+          <t>12,91; 27,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 35,5</t>
+          <t>14,26; 35,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 350,81</t>
+          <t>7,92; 45,56</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,57</t>
+          <t>1,51; 13,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 17,63</t>
+          <t>3,81; 17,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,5</t>
+          <t>4,14; 16,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,76</t>
+          <t>-3,11; 3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 50,47</t>
+          <t>4,4; 49,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 47,43</t>
+          <t>8,68; 47,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 55,74</t>
+          <t>12,09; 59,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 45,61</t>
+          <t>-23,7; 44,46</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,68</t>
+          <t>3,04; 7,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,23</t>
+          <t>4,38; 9,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,86</t>
+          <t>5,33; 9,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 24,2</t>
+          <t>2,52; 5,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 27,4</t>
+          <t>10,01; 28,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 21,22</t>
+          <t>9,51; 21,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 32,53</t>
+          <t>16,57; 33,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,67; 219,91</t>
+          <t>17,16; 47,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
